--- a/tracking_forms/001_shipping_load_report_form--tracking_forms.xlsx
+++ b/tracking_forms/001_shipping_load_report_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John Doe', 'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane Doe', 'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'joe_doe',_'value':_'joe_doe'}</t>
+          <t>joe_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Joe Doe', 'value': 'Joe Doe'}</t>
+          <t>Joe Doe</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'nyc',_'value':_'nyc'}</t>
+          <t>nyc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'NYC', 'value': 'NYC'}</t>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lax',_'value':_'lax'}</t>
+          <t>lax</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'LAX', 'value': 'LAX'}</t>
+          <t>LAX</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jfk',_'value':_'jfk'}</t>
+          <t>jfk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'JFK', 'value': 'JFK'}</t>
+          <t>JFK</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_transit',_'value':_'in_transit'}</t>
+          <t>in_transit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Transit', 'value': 'In Transit'}</t>
+          <t>In Transit</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'delivered',_'value':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Delivered', 'value': 'Delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'picked_up',_'value':_'picked_up'}</t>
+          <t>picked_up</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Picked Up', 'value': 'Picked Up'}</t>
+          <t>Picked Up</t>
         </is>
       </c>
     </row>
